--- a/data/derived_data/2_RarefyData/ps_16Sm_sq_tax_table.xlsx
+++ b/data/derived_data/2_RarefyData/ps_16Sm_sq_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="1374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="1375">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -2460,6 +2460,9 @@
   </si>
   <si>
     <t xml:space="preserve">Cluster_337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tatumella</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_338</t>
@@ -11970,7 +11973,7 @@
         <v>49</v>
       </c>
       <c r="G289" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H289" t="s">
         <v>229</v>
@@ -17950,7 +17953,7 @@
         <v>53</v>
       </c>
       <c r="G519" t="s">
-        <v>15</v>
+        <v>816</v>
       </c>
       <c r="H519" t="s">
         <v>15</v>
@@ -17958,7 +17961,7 @@
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B520" t="s">
         <v>9</v>
@@ -17976,15 +17979,15 @@
         <v>443</v>
       </c>
       <c r="G520" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H520" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B521" t="s">
         <v>9</v>
@@ -18002,7 +18005,7 @@
         <v>221</v>
       </c>
       <c r="G521" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H521" t="s">
         <v>15</v>
@@ -18010,7 +18013,7 @@
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B522" t="s">
         <v>9</v>
@@ -18036,7 +18039,7 @@
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B523" t="s">
         <v>9</v>
@@ -18062,7 +18065,7 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B524" t="s">
         <v>9</v>
@@ -18088,7 +18091,7 @@
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B525" t="s">
         <v>9</v>
@@ -18106,7 +18109,7 @@
         <v>176</v>
       </c>
       <c r="G525" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H525" t="s">
         <v>15</v>
@@ -18114,7 +18117,7 @@
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B526" t="s">
         <v>9</v>
@@ -18140,7 +18143,7 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B527" t="s">
         <v>9</v>
@@ -18166,7 +18169,7 @@
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B528" t="s">
         <v>9</v>
@@ -18192,7 +18195,7 @@
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B529" t="s">
         <v>9</v>
@@ -18218,7 +18221,7 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B530" t="s">
         <v>9</v>
@@ -18244,7 +18247,7 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B531" t="s">
         <v>9</v>
@@ -18270,7 +18273,7 @@
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B532" t="s">
         <v>9</v>
@@ -18296,7 +18299,7 @@
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B533" t="s">
         <v>9</v>
@@ -18314,7 +18317,7 @@
         <v>86</v>
       </c>
       <c r="G533" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H533" t="s">
         <v>15</v>
@@ -18322,7 +18325,7 @@
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B534" t="s">
         <v>9</v>
@@ -18348,7 +18351,7 @@
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B535" t="s">
         <v>9</v>
@@ -18374,7 +18377,7 @@
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B536" t="s">
         <v>9</v>
@@ -18400,7 +18403,7 @@
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B537" t="s">
         <v>9</v>
@@ -18426,7 +18429,7 @@
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B538" t="s">
         <v>9</v>
@@ -18452,7 +18455,7 @@
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B539" t="s">
         <v>9</v>
@@ -18478,7 +18481,7 @@
     </row>
     <row r="540">
       <c r="A540" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B540" t="s">
         <v>9</v>
@@ -18504,7 +18507,7 @@
     </row>
     <row r="541">
       <c r="A541" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B541" t="s">
         <v>9</v>
@@ -18530,7 +18533,7 @@
     </row>
     <row r="542">
       <c r="A542" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B542" t="s">
         <v>9</v>
@@ -18556,7 +18559,7 @@
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B543" t="s">
         <v>9</v>
@@ -18582,7 +18585,7 @@
     </row>
     <row r="544">
       <c r="A544" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B544" t="s">
         <v>9</v>
@@ -18608,7 +18611,7 @@
     </row>
     <row r="545">
       <c r="A545" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B545" t="s">
         <v>9</v>
@@ -18634,7 +18637,7 @@
     </row>
     <row r="546">
       <c r="A546" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B546" t="s">
         <v>9</v>
@@ -18660,7 +18663,7 @@
     </row>
     <row r="547">
       <c r="A547" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B547" t="s">
         <v>9</v>
@@ -18686,7 +18689,7 @@
     </row>
     <row r="548">
       <c r="A548" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B548" t="s">
         <v>9</v>
@@ -18712,7 +18715,7 @@
     </row>
     <row r="549">
       <c r="A549" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B549" t="s">
         <v>9</v>
@@ -18738,7 +18741,7 @@
     </row>
     <row r="550">
       <c r="A550" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B550" t="s">
         <v>9</v>
@@ -18764,7 +18767,7 @@
     </row>
     <row r="551">
       <c r="A551" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B551" t="s">
         <v>9</v>
@@ -18790,7 +18793,7 @@
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B552" t="s">
         <v>9</v>
@@ -18816,7 +18819,7 @@
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B553" t="s">
         <v>9</v>
@@ -18842,7 +18845,7 @@
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B554" t="s">
         <v>9</v>
@@ -18868,7 +18871,7 @@
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B555" t="s">
         <v>9</v>
@@ -18894,7 +18897,7 @@
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B556" t="s">
         <v>9</v>
@@ -18920,7 +18923,7 @@
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B557" t="s">
         <v>9</v>
@@ -18946,7 +18949,7 @@
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B558" t="s">
         <v>9</v>
@@ -18964,7 +18967,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H558" t="s">
         <v>15</v>
@@ -18972,7 +18975,7 @@
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B559" t="s">
         <v>9</v>
@@ -18998,7 +19001,7 @@
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B560" t="s">
         <v>9</v>
@@ -19024,7 +19027,7 @@
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B561" t="s">
         <v>9</v>
@@ -19050,7 +19053,7 @@
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B562" t="s">
         <v>9</v>
@@ -19076,7 +19079,7 @@
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B563" t="s">
         <v>9</v>
@@ -19102,7 +19105,7 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B564" t="s">
         <v>9</v>
@@ -19117,7 +19120,7 @@
         <v>352</v>
       </c>
       <c r="F564" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G564" t="s">
         <v>15</v>
@@ -19128,7 +19131,7 @@
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B565" t="s">
         <v>9</v>
@@ -19154,7 +19157,7 @@
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B566" t="s">
         <v>9</v>
@@ -19180,7 +19183,7 @@
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B567" t="s">
         <v>9</v>
@@ -19192,10 +19195,10 @@
         <v>11</v>
       </c>
       <c r="E567" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F567" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G567" t="s">
         <v>15</v>
@@ -19206,7 +19209,7 @@
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B568" t="s">
         <v>9</v>
@@ -19232,7 +19235,7 @@
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B569" t="s">
         <v>9</v>
@@ -19258,7 +19261,7 @@
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B570" t="s">
         <v>9</v>
@@ -19273,10 +19276,10 @@
         <v>77</v>
       </c>
       <c r="F570" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G570" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H570" t="s">
         <v>15</v>
@@ -19284,7 +19287,7 @@
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B571" t="s">
         <v>9</v>
@@ -19310,7 +19313,7 @@
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B572" t="s">
         <v>9</v>
@@ -19336,7 +19339,7 @@
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B573" t="s">
         <v>9</v>
@@ -19357,12 +19360,12 @@
         <v>172</v>
       </c>
       <c r="H573" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B574" t="s">
         <v>9</v>
@@ -19388,7 +19391,7 @@
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B575" t="s">
         <v>9</v>
@@ -19414,7 +19417,7 @@
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B576" t="s">
         <v>9</v>
@@ -19440,7 +19443,7 @@
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B577" t="s">
         <v>9</v>
@@ -19466,7 +19469,7 @@
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B578" t="s">
         <v>9</v>
@@ -19492,7 +19495,7 @@
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B579" t="s">
         <v>9</v>
@@ -19507,10 +19510,10 @@
         <v>77</v>
       </c>
       <c r="F579" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="G579" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H579" t="s">
         <v>15</v>
@@ -19518,7 +19521,7 @@
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B580" t="s">
         <v>9</v>
@@ -19544,7 +19547,7 @@
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B581" t="s">
         <v>9</v>
@@ -19570,7 +19573,7 @@
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B582" t="s">
         <v>9</v>
@@ -19596,7 +19599,7 @@
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B583" t="s">
         <v>9</v>
@@ -19622,7 +19625,7 @@
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B584" t="s">
         <v>9</v>
@@ -19648,7 +19651,7 @@
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B585" t="s">
         <v>9</v>
@@ -19669,12 +19672,12 @@
         <v>50</v>
       </c>
       <c r="H585" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B586" t="s">
         <v>9</v>
@@ -19700,7 +19703,7 @@
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B587" t="s">
         <v>9</v>
@@ -19726,7 +19729,7 @@
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B588" t="s">
         <v>9</v>
@@ -19752,7 +19755,7 @@
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B589" t="s">
         <v>9</v>
@@ -19778,7 +19781,7 @@
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B590" t="s">
         <v>9</v>
@@ -19799,12 +19802,12 @@
         <v>40</v>
       </c>
       <c r="H590" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B591" t="s">
         <v>9</v>
@@ -19830,7 +19833,7 @@
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B592" t="s">
         <v>9</v>
@@ -19856,7 +19859,7 @@
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B593" t="s">
         <v>9</v>
@@ -19882,7 +19885,7 @@
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B594" t="s">
         <v>9</v>
@@ -19908,7 +19911,7 @@
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B595" t="s">
         <v>9</v>
@@ -19934,7 +19937,7 @@
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B596" t="s">
         <v>9</v>
@@ -19960,7 +19963,7 @@
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B597" t="s">
         <v>9</v>
@@ -19986,7 +19989,7 @@
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B598" t="s">
         <v>9</v>
@@ -20012,7 +20015,7 @@
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B599" t="s">
         <v>9</v>
@@ -20038,7 +20041,7 @@
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B600" t="s">
         <v>9</v>
@@ -20064,7 +20067,7 @@
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B601" t="s">
         <v>9</v>
@@ -20090,7 +20093,7 @@
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B602" t="s">
         <v>9</v>
@@ -20116,7 +20119,7 @@
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B603" t="s">
         <v>9</v>
@@ -20137,12 +20140,12 @@
         <v>15</v>
       </c>
       <c r="H603" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B604" t="s">
         <v>9</v>
@@ -20168,25 +20171,25 @@
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B605" t="s">
         <v>9</v>
       </c>
       <c r="C605" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D605" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E605" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="F605" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="G605" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H605" t="s">
         <v>15</v>
@@ -20194,7 +20197,7 @@
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B606" t="s">
         <v>9</v>
@@ -20220,7 +20223,7 @@
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B607" t="s">
         <v>9</v>
@@ -20246,7 +20249,7 @@
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B608" t="s">
         <v>9</v>
@@ -20272,7 +20275,7 @@
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B609" t="s">
         <v>9</v>
@@ -20298,7 +20301,7 @@
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B610" t="s">
         <v>9</v>
@@ -20324,7 +20327,7 @@
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B611" t="s">
         <v>9</v>
@@ -20350,7 +20353,7 @@
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B612" t="s">
         <v>9</v>
@@ -20376,7 +20379,7 @@
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B613" t="s">
         <v>9</v>
@@ -20397,12 +20400,12 @@
         <v>172</v>
       </c>
       <c r="H613" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B614" t="s">
         <v>9</v>
@@ -20428,7 +20431,7 @@
     </row>
     <row r="615">
       <c r="A615" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B615" t="s">
         <v>9</v>
@@ -20454,7 +20457,7 @@
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B616" t="s">
         <v>9</v>
@@ -20480,7 +20483,7 @@
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B617" t="s">
         <v>9</v>
@@ -20506,7 +20509,7 @@
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B618" t="s">
         <v>9</v>
@@ -20518,13 +20521,13 @@
         <v>70</v>
       </c>
       <c r="E618" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="F618" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="G618" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H618" t="s">
         <v>15</v>
@@ -20532,7 +20535,7 @@
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B619" t="s">
         <v>9</v>
@@ -20558,7 +20561,7 @@
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B620" t="s">
         <v>9</v>
@@ -20584,7 +20587,7 @@
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B621" t="s">
         <v>9</v>
@@ -20610,7 +20613,7 @@
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B622" t="s">
         <v>9</v>
@@ -20636,7 +20639,7 @@
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B623" t="s">
         <v>9</v>
@@ -20662,7 +20665,7 @@
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B624" t="s">
         <v>9</v>
@@ -20688,7 +20691,7 @@
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B625" t="s">
         <v>9</v>
@@ -20714,7 +20717,7 @@
     </row>
     <row r="626">
       <c r="A626" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B626" t="s">
         <v>9</v>
@@ -20740,7 +20743,7 @@
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B627" t="s">
         <v>9</v>
@@ -20766,7 +20769,7 @@
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B628" t="s">
         <v>9</v>
@@ -20792,7 +20795,7 @@
     </row>
     <row r="629">
       <c r="A629" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B629" t="s">
         <v>9</v>
@@ -20818,7 +20821,7 @@
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B630" t="s">
         <v>9</v>
@@ -20844,7 +20847,7 @@
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B631" t="s">
         <v>9</v>
@@ -20870,7 +20873,7 @@
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B632" t="s">
         <v>9</v>
@@ -20885,10 +20888,10 @@
         <v>12</v>
       </c>
       <c r="F632" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="G632" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H632" t="s">
         <v>15</v>
@@ -20896,7 +20899,7 @@
     </row>
     <row r="633">
       <c r="A633" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B633" t="s">
         <v>9</v>
@@ -20922,7 +20925,7 @@
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B634" t="s">
         <v>9</v>
@@ -20948,7 +20951,7 @@
     </row>
     <row r="635">
       <c r="A635" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B635" t="s">
         <v>9</v>
@@ -20974,7 +20977,7 @@
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B636" t="s">
         <v>9</v>
@@ -20989,10 +20992,10 @@
         <v>12</v>
       </c>
       <c r="F636" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="G636" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H636" t="s">
         <v>15</v>
@@ -21000,7 +21003,7 @@
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B637" t="s">
         <v>9</v>
@@ -21018,7 +21021,7 @@
         <v>5</v>
       </c>
       <c r="G637" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H637" t="s">
         <v>15</v>
@@ -21026,7 +21029,7 @@
     </row>
     <row r="638">
       <c r="A638" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B638" t="s">
         <v>9</v>
@@ -21052,7 +21055,7 @@
     </row>
     <row r="639">
       <c r="A639" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B639" t="s">
         <v>9</v>
@@ -21078,7 +21081,7 @@
     </row>
     <row r="640">
       <c r="A640" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B640" t="s">
         <v>9</v>
@@ -21104,7 +21107,7 @@
     </row>
     <row r="641">
       <c r="A641" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B641" t="s">
         <v>9</v>
@@ -21130,7 +21133,7 @@
     </row>
     <row r="642">
       <c r="A642" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B642" t="s">
         <v>9</v>
@@ -21156,7 +21159,7 @@
     </row>
     <row r="643">
       <c r="A643" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B643" t="s">
         <v>9</v>
@@ -21182,7 +21185,7 @@
     </row>
     <row r="644">
       <c r="A644" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B644" t="s">
         <v>9</v>
@@ -21197,18 +21200,18 @@
         <v>77</v>
       </c>
       <c r="F644" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G644" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H644" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B645" t="s">
         <v>9</v>
@@ -21234,7 +21237,7 @@
     </row>
     <row r="646">
       <c r="A646" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B646" t="s">
         <v>9</v>
@@ -21260,7 +21263,7 @@
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B647" t="s">
         <v>9</v>
@@ -21286,7 +21289,7 @@
     </row>
     <row r="648">
       <c r="A648" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B648" t="s">
         <v>9</v>
@@ -21312,7 +21315,7 @@
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B649" t="s">
         <v>9</v>
@@ -21333,12 +21336,12 @@
         <v>15</v>
       </c>
       <c r="H649" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B650" t="s">
         <v>9</v>
@@ -21364,7 +21367,7 @@
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B651" t="s">
         <v>9</v>
@@ -21390,7 +21393,7 @@
     </row>
     <row r="652">
       <c r="A652" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B652" t="s">
         <v>9</v>
@@ -21416,7 +21419,7 @@
     </row>
     <row r="653">
       <c r="A653" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B653" t="s">
         <v>9</v>
@@ -21442,7 +21445,7 @@
     </row>
     <row r="654">
       <c r="A654" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B654" t="s">
         <v>9</v>
@@ -21460,15 +21463,15 @@
         <v>279</v>
       </c>
       <c r="G654" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H654" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B655" t="s">
         <v>9</v>
@@ -21494,7 +21497,7 @@
     </row>
     <row r="656">
       <c r="A656" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B656" t="s">
         <v>9</v>
@@ -21520,7 +21523,7 @@
     </row>
     <row r="657">
       <c r="A657" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B657" t="s">
         <v>9</v>
@@ -21541,12 +21544,12 @@
         <v>15</v>
       </c>
       <c r="H657" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B658" t="s">
         <v>9</v>
@@ -21567,12 +21570,12 @@
         <v>40</v>
       </c>
       <c r="H658" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B659" t="s">
         <v>9</v>
@@ -21598,7 +21601,7 @@
     </row>
     <row r="660">
       <c r="A660" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B660" t="s">
         <v>9</v>
@@ -21624,7 +21627,7 @@
     </row>
     <row r="661">
       <c r="A661" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B661" t="s">
         <v>9</v>
@@ -21650,7 +21653,7 @@
     </row>
     <row r="662">
       <c r="A662" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B662" t="s">
         <v>9</v>
@@ -21676,7 +21679,7 @@
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B663" t="s">
         <v>9</v>
@@ -21702,7 +21705,7 @@
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B664" t="s">
         <v>9</v>
@@ -21728,7 +21731,7 @@
     </row>
     <row r="665">
       <c r="A665" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B665" t="s">
         <v>9</v>
@@ -21754,7 +21757,7 @@
     </row>
     <row r="666">
       <c r="A666" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B666" t="s">
         <v>9</v>
@@ -21780,7 +21783,7 @@
     </row>
     <row r="667">
       <c r="A667" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B667" t="s">
         <v>9</v>
@@ -21806,7 +21809,7 @@
     </row>
     <row r="668">
       <c r="A668" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B668" t="s">
         <v>9</v>
@@ -21832,7 +21835,7 @@
     </row>
     <row r="669">
       <c r="A669" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B669" t="s">
         <v>9</v>
@@ -21858,7 +21861,7 @@
     </row>
     <row r="670">
       <c r="A670" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B670" t="s">
         <v>9</v>
@@ -21884,7 +21887,7 @@
     </row>
     <row r="671">
       <c r="A671" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B671" t="s">
         <v>9</v>
@@ -21910,7 +21913,7 @@
     </row>
     <row r="672">
       <c r="A672" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B672" t="s">
         <v>9</v>
@@ -21936,7 +21939,7 @@
     </row>
     <row r="673">
       <c r="A673" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B673" t="s">
         <v>9</v>
@@ -21962,7 +21965,7 @@
     </row>
     <row r="674">
       <c r="A674" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B674" t="s">
         <v>9</v>
@@ -21980,7 +21983,7 @@
         <v>531</v>
       </c>
       <c r="G674" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H674" t="s">
         <v>15</v>
@@ -21988,7 +21991,7 @@
     </row>
     <row r="675">
       <c r="A675" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B675" t="s">
         <v>9</v>
@@ -22014,7 +22017,7 @@
     </row>
     <row r="676">
       <c r="A676" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B676" t="s">
         <v>9</v>
@@ -22040,7 +22043,7 @@
     </row>
     <row r="677">
       <c r="A677" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B677" t="s">
         <v>9</v>
@@ -22066,7 +22069,7 @@
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B678" t="s">
         <v>9</v>
@@ -22092,7 +22095,7 @@
     </row>
     <row r="679">
       <c r="A679" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B679" t="s">
         <v>9</v>
@@ -22118,7 +22121,7 @@
     </row>
     <row r="680">
       <c r="A680" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B680" t="s">
         <v>9</v>
@@ -22144,7 +22147,7 @@
     </row>
     <row r="681">
       <c r="A681" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B681" t="s">
         <v>9</v>
@@ -22170,7 +22173,7 @@
     </row>
     <row r="682">
       <c r="A682" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B682" t="s">
         <v>9</v>
@@ -22196,7 +22199,7 @@
     </row>
     <row r="683">
       <c r="A683" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B683" t="s">
         <v>9</v>
@@ -22222,7 +22225,7 @@
     </row>
     <row r="684">
       <c r="A684" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B684" t="s">
         <v>9</v>
@@ -22248,7 +22251,7 @@
     </row>
     <row r="685">
       <c r="A685" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B685" t="s">
         <v>9</v>
@@ -22274,7 +22277,7 @@
     </row>
     <row r="686">
       <c r="A686" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B686" t="s">
         <v>9</v>
@@ -22292,7 +22295,7 @@
         <v>93</v>
       </c>
       <c r="G686" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H686" t="s">
         <v>15</v>
@@ -22300,7 +22303,7 @@
     </row>
     <row r="687">
       <c r="A687" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B687" t="s">
         <v>9</v>
@@ -22326,7 +22329,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B688" t="s">
         <v>9</v>
@@ -22352,7 +22355,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B689" t="s">
         <v>9</v>
@@ -22378,7 +22381,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B690" t="s">
         <v>9</v>
@@ -22404,7 +22407,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B691" t="s">
         <v>9</v>
@@ -22430,7 +22433,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B692" t="s">
         <v>9</v>
@@ -22456,7 +22459,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B693" t="s">
         <v>9</v>
@@ -22482,7 +22485,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B694" t="s">
         <v>9</v>
@@ -22494,10 +22497,10 @@
         <v>43</v>
       </c>
       <c r="E694" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F694" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="G694" t="s">
         <v>15</v>
@@ -22508,7 +22511,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B695" t="s">
         <v>9</v>
@@ -22534,7 +22537,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B696" t="s">
         <v>9</v>
@@ -22560,7 +22563,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B697" t="s">
         <v>9</v>
@@ -22586,7 +22589,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B698" t="s">
         <v>9</v>
@@ -22612,7 +22615,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B699" t="s">
         <v>9</v>
@@ -22638,7 +22641,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B700" t="s">
         <v>9</v>
@@ -22664,7 +22667,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B701" t="s">
         <v>9</v>
@@ -22690,7 +22693,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B702" t="s">
         <v>9</v>
@@ -22716,7 +22719,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B703" t="s">
         <v>9</v>
@@ -22742,7 +22745,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B704" t="s">
         <v>9</v>
@@ -22754,10 +22757,10 @@
         <v>43</v>
       </c>
       <c r="E704" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F704" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G704" t="s">
         <v>15</v>
@@ -22768,7 +22771,7 @@
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B705" t="s">
         <v>9</v>
@@ -22794,7 +22797,7 @@
     </row>
     <row r="706">
       <c r="A706" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B706" t="s">
         <v>9</v>
@@ -22820,7 +22823,7 @@
     </row>
     <row r="707">
       <c r="A707" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B707" t="s">
         <v>9</v>
@@ -22846,7 +22849,7 @@
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B708" t="s">
         <v>9</v>
@@ -22872,7 +22875,7 @@
     </row>
     <row r="709">
       <c r="A709" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B709" t="s">
         <v>9</v>
@@ -22898,7 +22901,7 @@
     </row>
     <row r="710">
       <c r="A710" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B710" t="s">
         <v>9</v>
@@ -22924,7 +22927,7 @@
     </row>
     <row r="711">
       <c r="A711" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B711" t="s">
         <v>9</v>
@@ -22939,18 +22942,18 @@
         <v>12</v>
       </c>
       <c r="F711" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="G711" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H711" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B712" t="s">
         <v>9</v>
@@ -22968,7 +22971,7 @@
         <v>13</v>
       </c>
       <c r="G712" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H712" t="s">
         <v>15</v>
@@ -22976,7 +22979,7 @@
     </row>
     <row r="713">
       <c r="A713" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B713" t="s">
         <v>9</v>
@@ -22994,7 +22997,7 @@
         <v>766</v>
       </c>
       <c r="G713" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H713" t="s">
         <v>15</v>
@@ -23002,7 +23005,7 @@
     </row>
     <row r="714">
       <c r="A714" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B714" t="s">
         <v>9</v>
@@ -23028,7 +23031,7 @@
     </row>
     <row r="715">
       <c r="A715" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B715" t="s">
         <v>9</v>
@@ -23054,7 +23057,7 @@
     </row>
     <row r="716">
       <c r="A716" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B716" t="s">
         <v>9</v>
@@ -23080,7 +23083,7 @@
     </row>
     <row r="717">
       <c r="A717" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B717" t="s">
         <v>9</v>
@@ -23106,7 +23109,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B718" t="s">
         <v>9</v>
@@ -23124,7 +23127,7 @@
         <v>53</v>
       </c>
       <c r="G718" t="s">
-        <v>15</v>
+        <v>816</v>
       </c>
       <c r="H718" t="s">
         <v>15</v>
@@ -23132,7 +23135,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B719" t="s">
         <v>9</v>
@@ -23153,12 +23156,12 @@
         <v>50</v>
       </c>
       <c r="H719" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B720" t="s">
         <v>9</v>
@@ -23184,7 +23187,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B721" t="s">
         <v>9</v>
@@ -23210,7 +23213,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B722" t="s">
         <v>9</v>
@@ -23236,7 +23239,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B723" t="s">
         <v>9</v>
@@ -23262,7 +23265,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B724" t="s">
         <v>9</v>
@@ -23288,7 +23291,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B725" t="s">
         <v>9</v>
@@ -23314,7 +23317,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B726" t="s">
         <v>9</v>
@@ -23335,12 +23338,12 @@
         <v>50</v>
       </c>
       <c r="H726" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B727" t="s">
         <v>9</v>
@@ -23366,7 +23369,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B728" t="s">
         <v>9</v>
@@ -23392,7 +23395,7 @@
     </row>
     <row r="729">
       <c r="A729" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B729" t="s">
         <v>9</v>
@@ -23418,7 +23421,7 @@
     </row>
     <row r="730">
       <c r="A730" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B730" t="s">
         <v>9</v>
@@ -23444,7 +23447,7 @@
     </row>
     <row r="731">
       <c r="A731" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B731" t="s">
         <v>9</v>
@@ -23470,7 +23473,7 @@
     </row>
     <row r="732">
       <c r="A732" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B732" t="s">
         <v>9</v>
@@ -23496,7 +23499,7 @@
     </row>
     <row r="733">
       <c r="A733" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B733" t="s">
         <v>9</v>
@@ -23522,7 +23525,7 @@
     </row>
     <row r="734">
       <c r="A734" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B734" t="s">
         <v>9</v>
@@ -23548,7 +23551,7 @@
     </row>
     <row r="735">
       <c r="A735" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B735" t="s">
         <v>9</v>
@@ -23574,7 +23577,7 @@
     </row>
     <row r="736">
       <c r="A736" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B736" t="s">
         <v>9</v>
@@ -23589,10 +23592,10 @@
         <v>530</v>
       </c>
       <c r="F736" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="G736" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H736" t="s">
         <v>15</v>
@@ -23600,7 +23603,7 @@
     </row>
     <row r="737">
       <c r="A737" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B737" t="s">
         <v>9</v>
@@ -23626,7 +23629,7 @@
     </row>
     <row r="738">
       <c r="A738" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B738" t="s">
         <v>9</v>
@@ -23652,7 +23655,7 @@
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B739" t="s">
         <v>9</v>
@@ -23678,7 +23681,7 @@
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B740" t="s">
         <v>9</v>
@@ -23704,7 +23707,7 @@
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B741" t="s">
         <v>9</v>
@@ -23730,7 +23733,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B742" t="s">
         <v>9</v>
@@ -23756,7 +23759,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B743" t="s">
         <v>9</v>
@@ -23777,12 +23780,12 @@
         <v>671</v>
       </c>
       <c r="H743" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B744" t="s">
         <v>9</v>
@@ -23800,7 +23803,7 @@
         <v>200</v>
       </c>
       <c r="G744" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H744" t="s">
         <v>15</v>
@@ -23808,7 +23811,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B745" t="s">
         <v>9</v>
@@ -23834,7 +23837,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B746" t="s">
         <v>9</v>
@@ -23860,7 +23863,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B747" t="s">
         <v>9</v>
@@ -23878,7 +23881,7 @@
         <v>130</v>
       </c>
       <c r="G747" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H747" t="s">
         <v>15</v>
@@ -23886,7 +23889,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B748" t="s">
         <v>9</v>
@@ -23912,7 +23915,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B749" t="s">
         <v>9</v>
@@ -23938,7 +23941,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B750" t="s">
         <v>9</v>
@@ -23964,7 +23967,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B751" t="s">
         <v>15</v>
@@ -23990,7 +23993,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B752" t="s">
         <v>9</v>
@@ -24011,12 +24014,12 @@
         <v>15</v>
       </c>
       <c r="H752" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B753" t="s">
         <v>9</v>
@@ -24042,7 +24045,7 @@
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B754" t="s">
         <v>9</v>
@@ -24068,7 +24071,7 @@
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B755" t="s">
         <v>9</v>
@@ -24094,7 +24097,7 @@
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B756" t="s">
         <v>9</v>
@@ -24120,7 +24123,7 @@
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B757" t="s">
         <v>9</v>
@@ -24146,7 +24149,7 @@
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B758" t="s">
         <v>9</v>
@@ -24172,7 +24175,7 @@
     </row>
     <row r="759">
       <c r="A759" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B759" t="s">
         <v>9</v>
@@ -24190,7 +24193,7 @@
         <v>61</v>
       </c>
       <c r="G759" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H759" t="s">
         <v>15</v>
@@ -24198,7 +24201,7 @@
     </row>
     <row r="760">
       <c r="A760" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B760" t="s">
         <v>9</v>
@@ -24224,7 +24227,7 @@
     </row>
     <row r="761">
       <c r="A761" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B761" t="s">
         <v>9</v>
@@ -24245,12 +24248,12 @@
         <v>15</v>
       </c>
       <c r="H761" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B762" t="s">
         <v>9</v>
@@ -24276,7 +24279,7 @@
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B763" t="s">
         <v>9</v>
@@ -24302,7 +24305,7 @@
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B764" t="s">
         <v>9</v>
@@ -24328,7 +24331,7 @@
     </row>
     <row r="765">
       <c r="A765" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B765" t="s">
         <v>9</v>
@@ -24354,7 +24357,7 @@
     </row>
     <row r="766">
       <c r="A766" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B766" t="s">
         <v>9</v>
@@ -24380,7 +24383,7 @@
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B767" t="s">
         <v>9</v>
@@ -24406,7 +24409,7 @@
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B768" t="s">
         <v>9</v>
@@ -24432,7 +24435,7 @@
     </row>
     <row r="769">
       <c r="A769" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B769" t="s">
         <v>9</v>
@@ -24458,7 +24461,7 @@
     </row>
     <row r="770">
       <c r="A770" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B770" t="s">
         <v>9</v>
@@ -24484,7 +24487,7 @@
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B771" t="s">
         <v>9</v>
@@ -24510,7 +24513,7 @@
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B772" t="s">
         <v>9</v>
@@ -24536,7 +24539,7 @@
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B773" t="s">
         <v>9</v>
@@ -24562,7 +24565,7 @@
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B774" t="s">
         <v>9</v>
@@ -24588,7 +24591,7 @@
     </row>
     <row r="775">
       <c r="A775" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B775" t="s">
         <v>9</v>
@@ -24614,7 +24617,7 @@
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B776" t="s">
         <v>9</v>
@@ -24640,7 +24643,7 @@
     </row>
     <row r="777">
       <c r="A777" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B777" t="s">
         <v>9</v>
@@ -24666,7 +24669,7 @@
     </row>
     <row r="778">
       <c r="A778" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B778" t="s">
         <v>9</v>
@@ -24692,22 +24695,22 @@
     </row>
     <row r="779">
       <c r="A779" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B779" t="s">
         <v>9</v>
       </c>
       <c r="C779" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D779" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E779" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F779" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G779" t="s">
         <v>15</v>
@@ -24718,7 +24721,7 @@
     </row>
     <row r="780">
       <c r="A780" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B780" t="s">
         <v>9</v>
@@ -24744,7 +24747,7 @@
     </row>
     <row r="781">
       <c r="A781" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B781" t="s">
         <v>9</v>
@@ -24770,7 +24773,7 @@
     </row>
     <row r="782">
       <c r="A782" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B782" t="s">
         <v>9</v>
@@ -24796,7 +24799,7 @@
     </row>
     <row r="783">
       <c r="A783" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B783" t="s">
         <v>9</v>
@@ -24822,7 +24825,7 @@
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B784" t="s">
         <v>9</v>
@@ -24848,7 +24851,7 @@
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B785" t="s">
         <v>15</v>
@@ -24874,7 +24877,7 @@
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B786" t="s">
         <v>9</v>
@@ -24900,7 +24903,7 @@
     </row>
     <row r="787">
       <c r="A787" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B787" t="s">
         <v>9</v>
@@ -24926,7 +24929,7 @@
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B788" t="s">
         <v>9</v>
@@ -24952,7 +24955,7 @@
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B789" t="s">
         <v>9</v>
@@ -24970,7 +24973,7 @@
         <v>100</v>
       </c>
       <c r="G789" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H789" t="s">
         <v>15</v>
@@ -24978,7 +24981,7 @@
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B790" t="s">
         <v>9</v>
@@ -25004,7 +25007,7 @@
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B791" t="s">
         <v>9</v>
@@ -25030,7 +25033,7 @@
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B792" t="s">
         <v>9</v>
@@ -25056,7 +25059,7 @@
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B793" t="s">
         <v>9</v>
@@ -25082,7 +25085,7 @@
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B794" t="s">
         <v>9</v>
@@ -25108,7 +25111,7 @@
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B795" t="s">
         <v>9</v>
@@ -25134,7 +25137,7 @@
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B796" t="s">
         <v>9</v>
@@ -25160,7 +25163,7 @@
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B797" t="s">
         <v>9</v>
@@ -25186,7 +25189,7 @@
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B798" t="s">
         <v>9</v>
@@ -25212,7 +25215,7 @@
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B799" t="s">
         <v>9</v>
@@ -25238,7 +25241,7 @@
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B800" t="s">
         <v>9</v>
@@ -25264,7 +25267,7 @@
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B801" t="s">
         <v>9</v>
@@ -25290,7 +25293,7 @@
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B802" t="s">
         <v>9</v>
@@ -25316,7 +25319,7 @@
     </row>
     <row r="803">
       <c r="A803" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B803" t="s">
         <v>9</v>
@@ -25342,7 +25345,7 @@
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B804" t="s">
         <v>9</v>
@@ -25368,7 +25371,7 @@
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B805" t="s">
         <v>9</v>
@@ -25386,7 +25389,7 @@
         <v>200</v>
       </c>
       <c r="G805" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H805" t="s">
         <v>15</v>
@@ -25394,7 +25397,7 @@
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B806" t="s">
         <v>9</v>
@@ -25420,7 +25423,7 @@
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B807" t="s">
         <v>9</v>
@@ -25429,16 +25432,16 @@
         <v>75</v>
       </c>
       <c r="D807" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="E807" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F807" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="G807" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H807" t="s">
         <v>15</v>
@@ -25446,7 +25449,7 @@
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B808" t="s">
         <v>9</v>
@@ -25464,7 +25467,7 @@
         <v>248</v>
       </c>
       <c r="G808" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H808" t="s">
         <v>15</v>
@@ -25472,7 +25475,7 @@
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B809" t="s">
         <v>9</v>
@@ -25498,7 +25501,7 @@
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B810" t="s">
         <v>9</v>
@@ -25524,7 +25527,7 @@
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B811" t="s">
         <v>9</v>
@@ -25539,10 +25542,10 @@
         <v>12</v>
       </c>
       <c r="F811" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="G811" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H811" t="s">
         <v>15</v>
@@ -25550,7 +25553,7 @@
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B812" t="s">
         <v>9</v>
@@ -25576,7 +25579,7 @@
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B813" t="s">
         <v>9</v>
@@ -25602,7 +25605,7 @@
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B814" t="s">
         <v>9</v>
@@ -25620,7 +25623,7 @@
         <v>86</v>
       </c>
       <c r="G814" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H814" t="s">
         <v>15</v>
@@ -25628,7 +25631,7 @@
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B815" t="s">
         <v>9</v>
@@ -25654,7 +25657,7 @@
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B816" t="s">
         <v>9</v>
@@ -25672,7 +25675,7 @@
         <v>78</v>
       </c>
       <c r="G816" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H816" t="s">
         <v>15</v>
@@ -25680,7 +25683,7 @@
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B817" t="s">
         <v>9</v>
@@ -25706,7 +25709,7 @@
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B818" t="s">
         <v>9</v>
@@ -25732,7 +25735,7 @@
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B819" t="s">
         <v>9</v>
@@ -25758,7 +25761,7 @@
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B820" t="s">
         <v>9</v>
@@ -25784,7 +25787,7 @@
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B821" t="s">
         <v>9</v>
@@ -25810,7 +25813,7 @@
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B822" t="s">
         <v>9</v>
@@ -25836,7 +25839,7 @@
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B823" t="s">
         <v>9</v>
@@ -25862,7 +25865,7 @@
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B824" t="s">
         <v>9</v>
@@ -25888,7 +25891,7 @@
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B825" t="s">
         <v>9</v>
@@ -25914,7 +25917,7 @@
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B826" t="s">
         <v>9</v>
@@ -25932,7 +25935,7 @@
         <v>61</v>
       </c>
       <c r="G826" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H826" t="s">
         <v>15</v>
@@ -25940,7 +25943,7 @@
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B827" t="s">
         <v>9</v>
@@ -25966,7 +25969,7 @@
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B828" t="s">
         <v>9</v>
@@ -25992,7 +25995,7 @@
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B829" t="s">
         <v>9</v>
@@ -26018,7 +26021,7 @@
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B830" t="s">
         <v>9</v>
@@ -26044,7 +26047,7 @@
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B831" t="s">
         <v>9</v>
@@ -26070,7 +26073,7 @@
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B832" t="s">
         <v>9</v>
@@ -26096,7 +26099,7 @@
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B833" t="s">
         <v>9</v>
@@ -26122,7 +26125,7 @@
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B834" t="s">
         <v>9</v>
@@ -26148,7 +26151,7 @@
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B835" t="s">
         <v>9</v>
@@ -26174,7 +26177,7 @@
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B836" t="s">
         <v>9</v>
@@ -26200,7 +26203,7 @@
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B837" t="s">
         <v>9</v>
@@ -26226,7 +26229,7 @@
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B838" t="s">
         <v>9</v>
@@ -26252,7 +26255,7 @@
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B839" t="s">
         <v>9</v>
@@ -26278,7 +26281,7 @@
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B840" t="s">
         <v>9</v>
@@ -26304,7 +26307,7 @@
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B841" t="s">
         <v>9</v>
@@ -26330,7 +26333,7 @@
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B842" t="s">
         <v>9</v>
@@ -26356,7 +26359,7 @@
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B843" t="s">
         <v>9</v>
@@ -26382,7 +26385,7 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B844" t="s">
         <v>9</v>
@@ -26408,7 +26411,7 @@
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B845" t="s">
         <v>9</v>
@@ -26434,7 +26437,7 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B846" t="s">
         <v>9</v>
@@ -26446,13 +26449,13 @@
         <v>76</v>
       </c>
       <c r="E846" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="F846" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="G846" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H846" t="s">
         <v>15</v>
@@ -26460,7 +26463,7 @@
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B847" t="s">
         <v>9</v>
@@ -26486,7 +26489,7 @@
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B848" t="s">
         <v>9</v>
@@ -26507,12 +26510,12 @@
         <v>15</v>
       </c>
       <c r="H848" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B849" t="s">
         <v>9</v>
@@ -26538,7 +26541,7 @@
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B850" t="s">
         <v>9</v>
@@ -26556,7 +26559,7 @@
         <v>415</v>
       </c>
       <c r="G850" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H850" t="s">
         <v>15</v>
@@ -26564,7 +26567,7 @@
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B851" t="s">
         <v>9</v>
@@ -26590,25 +26593,25 @@
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B852" t="s">
         <v>9</v>
       </c>
       <c r="C852" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="D852" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="E852" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="F852" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="G852" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H852" t="s">
         <v>15</v>
@@ -26616,7 +26619,7 @@
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B853" t="s">
         <v>9</v>
@@ -26642,7 +26645,7 @@
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B854" t="s">
         <v>9</v>
@@ -26668,7 +26671,7 @@
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B855" t="s">
         <v>9</v>
@@ -26694,7 +26697,7 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B856" t="s">
         <v>9</v>
@@ -26720,7 +26723,7 @@
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B857" t="s">
         <v>9</v>
@@ -26741,12 +26744,12 @@
         <v>360</v>
       </c>
       <c r="H857" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B858" t="s">
         <v>9</v>
@@ -26772,7 +26775,7 @@
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B859" t="s">
         <v>9</v>
@@ -26798,7 +26801,7 @@
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B860" t="s">
         <v>9</v>
@@ -26824,7 +26827,7 @@
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B861" t="s">
         <v>9</v>
@@ -26850,7 +26853,7 @@
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B862" t="s">
         <v>9</v>
@@ -26876,7 +26879,7 @@
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B863" t="s">
         <v>9</v>
@@ -26902,7 +26905,7 @@
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B864" t="s">
         <v>9</v>
@@ -26928,7 +26931,7 @@
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B865" t="s">
         <v>9</v>
@@ -26954,7 +26957,7 @@
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B866" t="s">
         <v>9</v>
@@ -26980,7 +26983,7 @@
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B867" t="s">
         <v>9</v>
@@ -27006,7 +27009,7 @@
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B868" t="s">
         <v>9</v>
@@ -27032,7 +27035,7 @@
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B869" t="s">
         <v>9</v>
@@ -27058,7 +27061,7 @@
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B870" t="s">
         <v>9</v>
@@ -27084,7 +27087,7 @@
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B871" t="s">
         <v>9</v>
@@ -27102,7 +27105,7 @@
         <v>176</v>
       </c>
       <c r="G871" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H871" t="s">
         <v>15</v>
@@ -27110,7 +27113,7 @@
     </row>
     <row r="872">
       <c r="A872" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B872" t="s">
         <v>9</v>
@@ -27136,7 +27139,7 @@
     </row>
     <row r="873">
       <c r="A873" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B873" t="s">
         <v>9</v>
@@ -27162,7 +27165,7 @@
     </row>
     <row r="874">
       <c r="A874" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B874" t="s">
         <v>9</v>
@@ -27180,7 +27183,7 @@
         <v>49</v>
       </c>
       <c r="G874" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H874" t="s">
         <v>15</v>
@@ -27188,7 +27191,7 @@
     </row>
     <row r="875">
       <c r="A875" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B875" t="s">
         <v>9</v>
@@ -27214,7 +27217,7 @@
     </row>
     <row r="876">
       <c r="A876" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B876" t="s">
         <v>9</v>
@@ -27240,7 +27243,7 @@
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B877" t="s">
         <v>9</v>
@@ -27266,7 +27269,7 @@
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B878" t="s">
         <v>9</v>
@@ -27287,12 +27290,12 @@
         <v>375</v>
       </c>
       <c r="H878" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B879" t="s">
         <v>9</v>
@@ -27318,7 +27321,7 @@
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B880" t="s">
         <v>9</v>
@@ -27344,7 +27347,7 @@
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B881" t="s">
         <v>9</v>
@@ -27365,12 +27368,12 @@
         <v>131</v>
       </c>
       <c r="H881" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B882" t="s">
         <v>9</v>
@@ -27396,7 +27399,7 @@
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B883" t="s">
         <v>9</v>
@@ -27422,7 +27425,7 @@
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B884" t="s">
         <v>9</v>
@@ -27448,7 +27451,7 @@
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B885" t="s">
         <v>9</v>
@@ -27474,7 +27477,7 @@
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B886" t="s">
         <v>9</v>
@@ -27500,7 +27503,7 @@
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B887" t="s">
         <v>9</v>
@@ -27521,12 +27524,12 @@
         <v>15</v>
       </c>
       <c r="H887" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B888" t="s">
         <v>9</v>
@@ -27552,7 +27555,7 @@
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B889" t="s">
         <v>9</v>
@@ -27578,7 +27581,7 @@
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B890" t="s">
         <v>9</v>
@@ -27604,7 +27607,7 @@
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B891" t="s">
         <v>9</v>
@@ -27630,7 +27633,7 @@
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B892" t="s">
         <v>9</v>
@@ -27656,7 +27659,7 @@
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B893" t="s">
         <v>9</v>
@@ -27682,25 +27685,25 @@
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B894" t="s">
         <v>9</v>
       </c>
       <c r="C894" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D894" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="E894" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="F894" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="G894" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H894" t="s">
         <v>15</v>
@@ -27708,7 +27711,7 @@
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B895" t="s">
         <v>9</v>
@@ -27734,7 +27737,7 @@
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B896" t="s">
         <v>9</v>
@@ -27760,7 +27763,7 @@
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B897" t="s">
         <v>9</v>
@@ -27786,7 +27789,7 @@
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B898" t="s">
         <v>9</v>
@@ -27812,7 +27815,7 @@
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B899" t="s">
         <v>9</v>
@@ -27838,7 +27841,7 @@
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B900" t="s">
         <v>9</v>
@@ -27864,7 +27867,7 @@
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B901" t="s">
         <v>9</v>
@@ -27882,7 +27885,7 @@
         <v>78</v>
       </c>
       <c r="G901" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H901" t="s">
         <v>15</v>
@@ -27890,7 +27893,7 @@
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B902" t="s">
         <v>9</v>
@@ -27916,7 +27919,7 @@
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B903" t="s">
         <v>9</v>
@@ -27942,7 +27945,7 @@
     </row>
     <row r="904">
       <c r="A904" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B904" t="s">
         <v>9</v>
@@ -27968,7 +27971,7 @@
     </row>
     <row r="905">
       <c r="A905" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B905" t="s">
         <v>9</v>
@@ -27994,7 +27997,7 @@
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B906" t="s">
         <v>9</v>
@@ -28006,10 +28009,10 @@
         <v>33</v>
       </c>
       <c r="E906" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="F906" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="G906" t="s">
         <v>15</v>
@@ -28020,7 +28023,7 @@
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B907" t="s">
         <v>9</v>
@@ -28046,7 +28049,7 @@
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B908" t="s">
         <v>9</v>
@@ -28072,7 +28075,7 @@
     </row>
     <row r="909">
       <c r="A909" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B909" t="s">
         <v>9</v>
@@ -28098,7 +28101,7 @@
     </row>
     <row r="910">
       <c r="A910" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B910" t="s">
         <v>9</v>
@@ -28124,7 +28127,7 @@
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B911" t="s">
         <v>9</v>
@@ -28150,7 +28153,7 @@
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B912" t="s">
         <v>9</v>
@@ -28176,7 +28179,7 @@
     </row>
     <row r="913">
       <c r="A913" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B913" t="s">
         <v>9</v>
@@ -28202,7 +28205,7 @@
     </row>
     <row r="914">
       <c r="A914" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B914" t="s">
         <v>9</v>
@@ -28228,7 +28231,7 @@
     </row>
     <row r="915">
       <c r="A915" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B915" t="s">
         <v>9</v>
@@ -28254,7 +28257,7 @@
     </row>
     <row r="916">
       <c r="A916" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B916" t="s">
         <v>9</v>
@@ -28280,7 +28283,7 @@
     </row>
     <row r="917">
       <c r="A917" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B917" t="s">
         <v>9</v>
@@ -28306,7 +28309,7 @@
     </row>
     <row r="918">
       <c r="A918" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B918" t="s">
         <v>9</v>
@@ -28332,7 +28335,7 @@
     </row>
     <row r="919">
       <c r="A919" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B919" t="s">
         <v>9</v>
@@ -28358,7 +28361,7 @@
     </row>
     <row r="920">
       <c r="A920" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B920" t="s">
         <v>9</v>
@@ -28370,10 +28373,10 @@
         <v>33</v>
       </c>
       <c r="E920" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="F920" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="G920" t="s">
         <v>15</v>
@@ -28384,7 +28387,7 @@
     </row>
     <row r="921">
       <c r="A921" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B921" t="s">
         <v>9</v>
@@ -28410,7 +28413,7 @@
     </row>
     <row r="922">
       <c r="A922" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B922" t="s">
         <v>9</v>
@@ -28436,7 +28439,7 @@
     </row>
     <row r="923">
       <c r="A923" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B923" t="s">
         <v>9</v>
@@ -28454,7 +28457,7 @@
         <v>241</v>
       </c>
       <c r="G923" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H923" t="s">
         <v>15</v>
@@ -28462,7 +28465,7 @@
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B924" t="s">
         <v>9</v>
@@ -28488,7 +28491,7 @@
     </row>
     <row r="925">
       <c r="A925" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B925" t="s">
         <v>9</v>
@@ -28514,7 +28517,7 @@
     </row>
     <row r="926">
       <c r="A926" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B926" t="s">
         <v>9</v>
@@ -28540,7 +28543,7 @@
     </row>
     <row r="927">
       <c r="A927" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B927" t="s">
         <v>9</v>
@@ -28566,7 +28569,7 @@
     </row>
     <row r="928">
       <c r="A928" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B928" t="s">
         <v>9</v>
@@ -28581,10 +28584,10 @@
         <v>12</v>
       </c>
       <c r="F928" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="G928" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H928" t="s">
         <v>15</v>
@@ -28592,7 +28595,7 @@
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B929" t="s">
         <v>9</v>
@@ -28618,7 +28621,7 @@
     </row>
     <row r="930">
       <c r="A930" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B930" t="s">
         <v>9</v>
@@ -28644,7 +28647,7 @@
     </row>
     <row r="931">
       <c r="A931" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B931" t="s">
         <v>9</v>
@@ -28670,7 +28673,7 @@
     </row>
     <row r="932">
       <c r="A932" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B932" t="s">
         <v>9</v>
@@ -28696,7 +28699,7 @@
     </row>
     <row r="933">
       <c r="A933" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B933" t="s">
         <v>9</v>
@@ -28722,7 +28725,7 @@
     </row>
     <row r="934">
       <c r="A934" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B934" t="s">
         <v>9</v>
@@ -28748,7 +28751,7 @@
     </row>
     <row r="935">
       <c r="A935" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B935" t="s">
         <v>9</v>
@@ -28774,7 +28777,7 @@
     </row>
     <row r="936">
       <c r="A936" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B936" t="s">
         <v>9</v>
@@ -28800,7 +28803,7 @@
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B937" t="s">
         <v>9</v>
@@ -28826,7 +28829,7 @@
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B938" t="s">
         <v>9</v>
@@ -28852,7 +28855,7 @@
     </row>
     <row r="939">
       <c r="A939" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B939" t="s">
         <v>9</v>
@@ -28870,7 +28873,7 @@
         <v>78</v>
       </c>
       <c r="G939" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H939" t="s">
         <v>15</v>
@@ -28878,7 +28881,7 @@
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B940" t="s">
         <v>9</v>
@@ -28904,7 +28907,7 @@
     </row>
     <row r="941">
       <c r="A941" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B941" t="s">
         <v>9</v>
@@ -28930,7 +28933,7 @@
     </row>
     <row r="942">
       <c r="A942" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B942" t="s">
         <v>9</v>
@@ -28956,7 +28959,7 @@
     </row>
     <row r="943">
       <c r="A943" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B943" t="s">
         <v>9</v>
@@ -28982,7 +28985,7 @@
     </row>
     <row r="944">
       <c r="A944" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B944" t="s">
         <v>9</v>
@@ -29008,7 +29011,7 @@
     </row>
     <row r="945">
       <c r="A945" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B945" t="s">
         <v>9</v>
@@ -29034,7 +29037,7 @@
     </row>
     <row r="946">
       <c r="A946" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B946" t="s">
         <v>9</v>
@@ -29060,7 +29063,7 @@
     </row>
     <row r="947">
       <c r="A947" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B947" t="s">
         <v>9</v>
@@ -29086,7 +29089,7 @@
     </row>
     <row r="948">
       <c r="A948" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B948" t="s">
         <v>9</v>
@@ -29112,7 +29115,7 @@
     </row>
     <row r="949">
       <c r="A949" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B949" t="s">
         <v>9</v>
@@ -29138,7 +29141,7 @@
     </row>
     <row r="950">
       <c r="A950" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B950" t="s">
         <v>9</v>
@@ -29164,7 +29167,7 @@
     </row>
     <row r="951">
       <c r="A951" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B951" t="s">
         <v>9</v>
@@ -29190,7 +29193,7 @@
     </row>
     <row r="952">
       <c r="A952" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B952" t="s">
         <v>9</v>
@@ -29216,7 +29219,7 @@
     </row>
     <row r="953">
       <c r="A953" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B953" t="s">
         <v>9</v>
@@ -29242,7 +29245,7 @@
     </row>
     <row r="954">
       <c r="A954" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B954" t="s">
         <v>9</v>
@@ -29268,7 +29271,7 @@
     </row>
     <row r="955">
       <c r="A955" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B955" t="s">
         <v>9</v>
@@ -29294,7 +29297,7 @@
     </row>
     <row r="956">
       <c r="A956" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B956" t="s">
         <v>9</v>
@@ -29320,7 +29323,7 @@
     </row>
     <row r="957">
       <c r="A957" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B957" t="s">
         <v>9</v>
@@ -29346,7 +29349,7 @@
     </row>
     <row r="958">
       <c r="A958" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B958" t="s">
         <v>9</v>
@@ -29372,7 +29375,7 @@
     </row>
     <row r="959">
       <c r="A959" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B959" t="s">
         <v>9</v>
@@ -29398,7 +29401,7 @@
     </row>
     <row r="960">
       <c r="A960" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B960" t="s">
         <v>9</v>
@@ -29424,7 +29427,7 @@
     </row>
     <row r="961">
       <c r="A961" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B961" t="s">
         <v>9</v>
@@ -29450,7 +29453,7 @@
     </row>
     <row r="962">
       <c r="A962" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B962" t="s">
         <v>9</v>
@@ -29468,7 +29471,7 @@
         <v>61</v>
       </c>
       <c r="G962" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H962" t="s">
         <v>15</v>
@@ -29476,7 +29479,7 @@
     </row>
     <row r="963">
       <c r="A963" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B963" t="s">
         <v>9</v>
@@ -29494,7 +29497,7 @@
         <v>49</v>
       </c>
       <c r="G963" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H963" t="s">
         <v>229</v>
@@ -29502,7 +29505,7 @@
     </row>
     <row r="964">
       <c r="A964" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B964" t="s">
         <v>9</v>
@@ -29528,7 +29531,7 @@
     </row>
     <row r="965">
       <c r="A965" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B965" t="s">
         <v>9</v>
@@ -29554,7 +29557,7 @@
     </row>
     <row r="966">
       <c r="A966" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B966" t="s">
         <v>9</v>
@@ -29572,7 +29575,7 @@
         <v>86</v>
       </c>
       <c r="G966" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H966" t="s">
         <v>15</v>
@@ -29580,7 +29583,7 @@
     </row>
     <row r="967">
       <c r="A967" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B967" t="s">
         <v>9</v>
@@ -29606,7 +29609,7 @@
     </row>
     <row r="968">
       <c r="A968" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B968" t="s">
         <v>9</v>
@@ -29632,7 +29635,7 @@
     </row>
     <row r="969">
       <c r="A969" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B969" t="s">
         <v>9</v>
@@ -29658,7 +29661,7 @@
     </row>
     <row r="970">
       <c r="A970" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B970" t="s">
         <v>9</v>
@@ -29684,7 +29687,7 @@
     </row>
     <row r="971">
       <c r="A971" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B971" t="s">
         <v>9</v>
@@ -29710,7 +29713,7 @@
     </row>
     <row r="972">
       <c r="A972" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B972" t="s">
         <v>9</v>
@@ -29736,7 +29739,7 @@
     </row>
     <row r="973">
       <c r="A973" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B973" t="s">
         <v>9</v>
@@ -29762,7 +29765,7 @@
     </row>
     <row r="974">
       <c r="A974" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B974" t="s">
         <v>9</v>
@@ -29788,7 +29791,7 @@
     </row>
     <row r="975">
       <c r="A975" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B975" t="s">
         <v>9</v>
@@ -29814,7 +29817,7 @@
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B976" t="s">
         <v>9</v>
@@ -29840,7 +29843,7 @@
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B977" t="s">
         <v>9</v>
@@ -29866,7 +29869,7 @@
     </row>
     <row r="978">
       <c r="A978" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B978" t="s">
         <v>9</v>
@@ -29892,7 +29895,7 @@
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B979" t="s">
         <v>9</v>
@@ -29918,7 +29921,7 @@
     </row>
     <row r="980">
       <c r="A980" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B980" t="s">
         <v>9</v>
@@ -29944,7 +29947,7 @@
     </row>
     <row r="981">
       <c r="A981" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B981" t="s">
         <v>9</v>
@@ -29970,7 +29973,7 @@
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B982" t="s">
         <v>9</v>
@@ -29996,7 +29999,7 @@
     </row>
     <row r="983">
       <c r="A983" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B983" t="s">
         <v>9</v>
@@ -30022,7 +30025,7 @@
     </row>
     <row r="984">
       <c r="A984" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B984" t="s">
         <v>9</v>
@@ -30048,7 +30051,7 @@
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B985" t="s">
         <v>9</v>
@@ -30074,7 +30077,7 @@
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B986" t="s">
         <v>15</v>
@@ -30100,7 +30103,7 @@
     </row>
     <row r="987">
       <c r="A987" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B987" t="s">
         <v>9</v>
@@ -30126,7 +30129,7 @@
     </row>
     <row r="988">
       <c r="A988" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B988" t="s">
         <v>9</v>
@@ -30152,7 +30155,7 @@
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B989" t="s">
         <v>9</v>
@@ -30178,7 +30181,7 @@
     </row>
     <row r="990">
       <c r="A990" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B990" t="s">
         <v>9</v>

--- a/data/derived_data/2_RarefyData/ps_16Sm_sq_tax_table.xlsx
+++ b/data/derived_data/2_RarefyData/ps_16Sm_sq_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="1375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="1376">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -3492,6 +3492,9 @@
   </si>
   <si>
     <t xml:space="preserve">Cluster_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gluconobacter cerinus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_600</t>
@@ -9604,7 +9607,7 @@
         <v>52</v>
       </c>
       <c r="F198" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="G198" t="s">
         <v>15</v>
@@ -25418,12 +25421,12 @@
         <v>64</v>
       </c>
       <c r="H806" t="s">
-        <v>15</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B807" t="s">
         <v>9</v>
@@ -25432,16 +25435,16 @@
         <v>75</v>
       </c>
       <c r="D807" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E807" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="F807" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="G807" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H807" t="s">
         <v>15</v>
@@ -25449,7 +25452,7 @@
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B808" t="s">
         <v>9</v>
@@ -25467,7 +25470,7 @@
         <v>248</v>
       </c>
       <c r="G808" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H808" t="s">
         <v>15</v>
@@ -25475,7 +25478,7 @@
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B809" t="s">
         <v>9</v>
@@ -25501,7 +25504,7 @@
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B810" t="s">
         <v>9</v>
@@ -25527,7 +25530,7 @@
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B811" t="s">
         <v>9</v>
@@ -25553,7 +25556,7 @@
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B812" t="s">
         <v>9</v>
@@ -25579,7 +25582,7 @@
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B813" t="s">
         <v>9</v>
@@ -25605,7 +25608,7 @@
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B814" t="s">
         <v>9</v>
@@ -25623,7 +25626,7 @@
         <v>86</v>
       </c>
       <c r="G814" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H814" t="s">
         <v>15</v>
@@ -25631,7 +25634,7 @@
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B815" t="s">
         <v>9</v>
@@ -25657,7 +25660,7 @@
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B816" t="s">
         <v>9</v>
@@ -25675,7 +25678,7 @@
         <v>78</v>
       </c>
       <c r="G816" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H816" t="s">
         <v>15</v>
@@ -25683,7 +25686,7 @@
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B817" t="s">
         <v>9</v>
@@ -25709,7 +25712,7 @@
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B818" t="s">
         <v>9</v>
@@ -25735,7 +25738,7 @@
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B819" t="s">
         <v>9</v>
@@ -25761,7 +25764,7 @@
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B820" t="s">
         <v>9</v>
@@ -25787,7 +25790,7 @@
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B821" t="s">
         <v>9</v>
@@ -25813,7 +25816,7 @@
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B822" t="s">
         <v>9</v>
@@ -25839,7 +25842,7 @@
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B823" t="s">
         <v>9</v>
@@ -25865,7 +25868,7 @@
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B824" t="s">
         <v>9</v>
@@ -25891,7 +25894,7 @@
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B825" t="s">
         <v>9</v>
@@ -25917,7 +25920,7 @@
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B826" t="s">
         <v>9</v>
@@ -25943,7 +25946,7 @@
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B827" t="s">
         <v>9</v>
@@ -25969,7 +25972,7 @@
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B828" t="s">
         <v>9</v>
@@ -25995,7 +25998,7 @@
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B829" t="s">
         <v>9</v>
@@ -26021,7 +26024,7 @@
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B830" t="s">
         <v>9</v>
@@ -26047,7 +26050,7 @@
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B831" t="s">
         <v>9</v>
@@ -26073,7 +26076,7 @@
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B832" t="s">
         <v>9</v>
@@ -26099,7 +26102,7 @@
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B833" t="s">
         <v>9</v>
@@ -26125,7 +26128,7 @@
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B834" t="s">
         <v>9</v>
@@ -26151,7 +26154,7 @@
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B835" t="s">
         <v>9</v>
@@ -26177,7 +26180,7 @@
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B836" t="s">
         <v>9</v>
@@ -26203,7 +26206,7 @@
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B837" t="s">
         <v>9</v>
@@ -26229,7 +26232,7 @@
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B838" t="s">
         <v>9</v>
@@ -26255,7 +26258,7 @@
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B839" t="s">
         <v>9</v>
@@ -26281,7 +26284,7 @@
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B840" t="s">
         <v>9</v>
@@ -26307,7 +26310,7 @@
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B841" t="s">
         <v>9</v>
@@ -26333,7 +26336,7 @@
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B842" t="s">
         <v>9</v>
@@ -26359,7 +26362,7 @@
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B843" t="s">
         <v>9</v>
@@ -26385,7 +26388,7 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B844" t="s">
         <v>9</v>
@@ -26411,7 +26414,7 @@
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B845" t="s">
         <v>9</v>
@@ -26437,7 +26440,7 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B846" t="s">
         <v>9</v>
@@ -26449,13 +26452,13 @@
         <v>76</v>
       </c>
       <c r="E846" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="F846" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="G846" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H846" t="s">
         <v>15</v>
@@ -26463,7 +26466,7 @@
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B847" t="s">
         <v>9</v>
@@ -26489,7 +26492,7 @@
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B848" t="s">
         <v>9</v>
@@ -26510,12 +26513,12 @@
         <v>15</v>
       </c>
       <c r="H848" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B849" t="s">
         <v>9</v>
@@ -26541,7 +26544,7 @@
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B850" t="s">
         <v>9</v>
@@ -26559,7 +26562,7 @@
         <v>415</v>
       </c>
       <c r="G850" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H850" t="s">
         <v>15</v>
@@ -26567,7 +26570,7 @@
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B851" t="s">
         <v>9</v>
@@ -26593,25 +26596,25 @@
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B852" t="s">
         <v>9</v>
       </c>
       <c r="C852" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="D852" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="E852" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="F852" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="G852" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H852" t="s">
         <v>15</v>
@@ -26619,7 +26622,7 @@
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B853" t="s">
         <v>9</v>
@@ -26645,7 +26648,7 @@
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B854" t="s">
         <v>9</v>
@@ -26671,7 +26674,7 @@
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B855" t="s">
         <v>9</v>
@@ -26697,7 +26700,7 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B856" t="s">
         <v>9</v>
@@ -26723,7 +26726,7 @@
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B857" t="s">
         <v>9</v>
@@ -26744,12 +26747,12 @@
         <v>360</v>
       </c>
       <c r="H857" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B858" t="s">
         <v>9</v>
@@ -26775,7 +26778,7 @@
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B859" t="s">
         <v>9</v>
@@ -26801,7 +26804,7 @@
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B860" t="s">
         <v>9</v>
@@ -26827,7 +26830,7 @@
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B861" t="s">
         <v>9</v>
@@ -26853,7 +26856,7 @@
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B862" t="s">
         <v>9</v>
@@ -26879,7 +26882,7 @@
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B863" t="s">
         <v>9</v>
@@ -26905,7 +26908,7 @@
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B864" t="s">
         <v>9</v>
@@ -26931,7 +26934,7 @@
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B865" t="s">
         <v>9</v>
@@ -26957,7 +26960,7 @@
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B866" t="s">
         <v>9</v>
@@ -26983,7 +26986,7 @@
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B867" t="s">
         <v>9</v>
@@ -27009,7 +27012,7 @@
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B868" t="s">
         <v>9</v>
@@ -27035,7 +27038,7 @@
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B869" t="s">
         <v>9</v>
@@ -27061,7 +27064,7 @@
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B870" t="s">
         <v>9</v>
@@ -27087,7 +27090,7 @@
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B871" t="s">
         <v>9</v>
@@ -27105,7 +27108,7 @@
         <v>176</v>
       </c>
       <c r="G871" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H871" t="s">
         <v>15</v>
@@ -27113,7 +27116,7 @@
     </row>
     <row r="872">
       <c r="A872" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B872" t="s">
         <v>9</v>
@@ -27139,7 +27142,7 @@
     </row>
     <row r="873">
       <c r="A873" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B873" t="s">
         <v>9</v>
@@ -27165,7 +27168,7 @@
     </row>
     <row r="874">
       <c r="A874" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B874" t="s">
         <v>9</v>
@@ -27183,7 +27186,7 @@
         <v>49</v>
       </c>
       <c r="G874" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="H874" t="s">
         <v>15</v>
@@ -27191,7 +27194,7 @@
     </row>
     <row r="875">
       <c r="A875" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B875" t="s">
         <v>9</v>
@@ -27217,7 +27220,7 @@
     </row>
     <row r="876">
       <c r="A876" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B876" t="s">
         <v>9</v>
@@ -27243,7 +27246,7 @@
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B877" t="s">
         <v>9</v>
@@ -27269,7 +27272,7 @@
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B878" t="s">
         <v>9</v>
@@ -27290,12 +27293,12 @@
         <v>375</v>
       </c>
       <c r="H878" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B879" t="s">
         <v>9</v>
@@ -27321,7 +27324,7 @@
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B880" t="s">
         <v>9</v>
@@ -27347,7 +27350,7 @@
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B881" t="s">
         <v>9</v>
@@ -27368,12 +27371,12 @@
         <v>131</v>
       </c>
       <c r="H881" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B882" t="s">
         <v>9</v>
@@ -27399,7 +27402,7 @@
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B883" t="s">
         <v>9</v>
@@ -27425,7 +27428,7 @@
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B884" t="s">
         <v>9</v>
@@ -27451,7 +27454,7 @@
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B885" t="s">
         <v>9</v>
@@ -27477,7 +27480,7 @@
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B886" t="s">
         <v>9</v>
@@ -27503,7 +27506,7 @@
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B887" t="s">
         <v>9</v>
@@ -27524,12 +27527,12 @@
         <v>15</v>
       </c>
       <c r="H887" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B888" t="s">
         <v>9</v>
@@ -27555,7 +27558,7 @@
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B889" t="s">
         <v>9</v>
@@ -27581,7 +27584,7 @@
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B890" t="s">
         <v>9</v>
@@ -27607,7 +27610,7 @@
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B891" t="s">
         <v>9</v>
@@ -27633,7 +27636,7 @@
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B892" t="s">
         <v>9</v>
@@ -27659,7 +27662,7 @@
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B893" t="s">
         <v>9</v>
@@ -27685,7 +27688,7 @@
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B894" t="s">
         <v>9</v>
@@ -27694,16 +27697,16 @@
         <v>1127</v>
       </c>
       <c r="D894" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="E894" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="F894" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="G894" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H894" t="s">
         <v>15</v>
@@ -27711,7 +27714,7 @@
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B895" t="s">
         <v>9</v>
@@ -27737,7 +27740,7 @@
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B896" t="s">
         <v>9</v>
@@ -27763,7 +27766,7 @@
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B897" t="s">
         <v>9</v>
@@ -27789,7 +27792,7 @@
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B898" t="s">
         <v>9</v>
@@ -27815,7 +27818,7 @@
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B899" t="s">
         <v>9</v>
@@ -27841,7 +27844,7 @@
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B900" t="s">
         <v>9</v>
@@ -27867,7 +27870,7 @@
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B901" t="s">
         <v>9</v>
@@ -27885,7 +27888,7 @@
         <v>78</v>
       </c>
       <c r="G901" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H901" t="s">
         <v>15</v>
@@ -27893,7 +27896,7 @@
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B902" t="s">
         <v>9</v>
@@ -27919,7 +27922,7 @@
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B903" t="s">
         <v>9</v>
@@ -27945,7 +27948,7 @@
     </row>
     <row r="904">
       <c r="A904" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B904" t="s">
         <v>9</v>
@@ -27971,7 +27974,7 @@
     </row>
     <row r="905">
       <c r="A905" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B905" t="s">
         <v>9</v>
@@ -27997,7 +28000,7 @@
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B906" t="s">
         <v>9</v>
@@ -28009,10 +28012,10 @@
         <v>33</v>
       </c>
       <c r="E906" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="F906" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G906" t="s">
         <v>15</v>
@@ -28023,7 +28026,7 @@
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B907" t="s">
         <v>9</v>
@@ -28049,7 +28052,7 @@
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B908" t="s">
         <v>9</v>
@@ -28075,7 +28078,7 @@
     </row>
     <row r="909">
       <c r="A909" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B909" t="s">
         <v>9</v>
@@ -28101,7 +28104,7 @@
     </row>
     <row r="910">
       <c r="A910" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B910" t="s">
         <v>9</v>
@@ -28127,7 +28130,7 @@
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B911" t="s">
         <v>9</v>
@@ -28153,7 +28156,7 @@
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B912" t="s">
         <v>9</v>
@@ -28179,7 +28182,7 @@
     </row>
     <row r="913">
       <c r="A913" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B913" t="s">
         <v>9</v>
@@ -28205,7 +28208,7 @@
     </row>
     <row r="914">
       <c r="A914" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B914" t="s">
         <v>9</v>
@@ -28231,7 +28234,7 @@
     </row>
     <row r="915">
       <c r="A915" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B915" t="s">
         <v>9</v>
@@ -28257,7 +28260,7 @@
     </row>
     <row r="916">
       <c r="A916" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B916" t="s">
         <v>9</v>
@@ -28283,7 +28286,7 @@
     </row>
     <row r="917">
       <c r="A917" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B917" t="s">
         <v>9</v>
@@ -28309,7 +28312,7 @@
     </row>
     <row r="918">
       <c r="A918" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B918" t="s">
         <v>9</v>
@@ -28335,7 +28338,7 @@
     </row>
     <row r="919">
       <c r="A919" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B919" t="s">
         <v>9</v>
@@ -28361,7 +28364,7 @@
     </row>
     <row r="920">
       <c r="A920" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B920" t="s">
         <v>9</v>
@@ -28373,10 +28376,10 @@
         <v>33</v>
       </c>
       <c r="E920" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="F920" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G920" t="s">
         <v>15</v>
@@ -28387,7 +28390,7 @@
     </row>
     <row r="921">
       <c r="A921" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B921" t="s">
         <v>9</v>
@@ -28413,7 +28416,7 @@
     </row>
     <row r="922">
       <c r="A922" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B922" t="s">
         <v>9</v>
@@ -28439,7 +28442,7 @@
     </row>
     <row r="923">
       <c r="A923" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B923" t="s">
         <v>9</v>
@@ -28457,7 +28460,7 @@
         <v>241</v>
       </c>
       <c r="G923" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H923" t="s">
         <v>15</v>
@@ -28465,7 +28468,7 @@
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B924" t="s">
         <v>9</v>
@@ -28491,7 +28494,7 @@
     </row>
     <row r="925">
       <c r="A925" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B925" t="s">
         <v>9</v>
@@ -28517,7 +28520,7 @@
     </row>
     <row r="926">
       <c r="A926" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B926" t="s">
         <v>9</v>
@@ -28543,7 +28546,7 @@
     </row>
     <row r="927">
       <c r="A927" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B927" t="s">
         <v>9</v>
@@ -28569,7 +28572,7 @@
     </row>
     <row r="928">
       <c r="A928" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B928" t="s">
         <v>9</v>
@@ -28595,7 +28598,7 @@
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B929" t="s">
         <v>9</v>
@@ -28621,7 +28624,7 @@
     </row>
     <row r="930">
       <c r="A930" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B930" t="s">
         <v>9</v>
@@ -28647,7 +28650,7 @@
     </row>
     <row r="931">
       <c r="A931" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B931" t="s">
         <v>9</v>
@@ -28673,7 +28676,7 @@
     </row>
     <row r="932">
       <c r="A932" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B932" t="s">
         <v>9</v>
@@ -28699,7 +28702,7 @@
     </row>
     <row r="933">
       <c r="A933" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B933" t="s">
         <v>9</v>
@@ -28725,7 +28728,7 @@
     </row>
     <row r="934">
       <c r="A934" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B934" t="s">
         <v>9</v>
@@ -28751,7 +28754,7 @@
     </row>
     <row r="935">
       <c r="A935" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B935" t="s">
         <v>9</v>
@@ -28777,7 +28780,7 @@
     </row>
     <row r="936">
       <c r="A936" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B936" t="s">
         <v>9</v>
@@ -28803,7 +28806,7 @@
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B937" t="s">
         <v>9</v>
@@ -28829,7 +28832,7 @@
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B938" t="s">
         <v>9</v>
@@ -28855,7 +28858,7 @@
     </row>
     <row r="939">
       <c r="A939" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B939" t="s">
         <v>9</v>
@@ -28873,7 +28876,7 @@
         <v>78</v>
       </c>
       <c r="G939" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H939" t="s">
         <v>15</v>
@@ -28881,7 +28884,7 @@
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B940" t="s">
         <v>9</v>
@@ -28907,7 +28910,7 @@
     </row>
     <row r="941">
       <c r="A941" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B941" t="s">
         <v>9</v>
@@ -28933,7 +28936,7 @@
     </row>
     <row r="942">
       <c r="A942" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B942" t="s">
         <v>9</v>
@@ -28959,7 +28962,7 @@
     </row>
     <row r="943">
       <c r="A943" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B943" t="s">
         <v>9</v>
@@ -28985,7 +28988,7 @@
     </row>
     <row r="944">
       <c r="A944" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B944" t="s">
         <v>9</v>
@@ -29011,7 +29014,7 @@
     </row>
     <row r="945">
       <c r="A945" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B945" t="s">
         <v>9</v>
@@ -29037,7 +29040,7 @@
     </row>
     <row r="946">
       <c r="A946" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B946" t="s">
         <v>9</v>
@@ -29063,7 +29066,7 @@
     </row>
     <row r="947">
       <c r="A947" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B947" t="s">
         <v>9</v>
@@ -29089,7 +29092,7 @@
     </row>
     <row r="948">
       <c r="A948" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B948" t="s">
         <v>9</v>
@@ -29115,7 +29118,7 @@
     </row>
     <row r="949">
       <c r="A949" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B949" t="s">
         <v>9</v>
@@ -29141,7 +29144,7 @@
     </row>
     <row r="950">
       <c r="A950" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B950" t="s">
         <v>9</v>
@@ -29167,7 +29170,7 @@
     </row>
     <row r="951">
       <c r="A951" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B951" t="s">
         <v>9</v>
@@ -29193,7 +29196,7 @@
     </row>
     <row r="952">
       <c r="A952" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B952" t="s">
         <v>9</v>
@@ -29219,7 +29222,7 @@
     </row>
     <row r="953">
       <c r="A953" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B953" t="s">
         <v>9</v>
@@ -29245,7 +29248,7 @@
     </row>
     <row r="954">
       <c r="A954" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B954" t="s">
         <v>9</v>
@@ -29271,7 +29274,7 @@
     </row>
     <row r="955">
       <c r="A955" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B955" t="s">
         <v>9</v>
@@ -29297,7 +29300,7 @@
     </row>
     <row r="956">
       <c r="A956" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B956" t="s">
         <v>9</v>
@@ -29323,7 +29326,7 @@
     </row>
     <row r="957">
       <c r="A957" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B957" t="s">
         <v>9</v>
@@ -29349,7 +29352,7 @@
     </row>
     <row r="958">
       <c r="A958" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B958" t="s">
         <v>9</v>
@@ -29375,7 +29378,7 @@
     </row>
     <row r="959">
       <c r="A959" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B959" t="s">
         <v>9</v>
@@ -29401,7 +29404,7 @@
     </row>
     <row r="960">
       <c r="A960" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B960" t="s">
         <v>9</v>
@@ -29427,7 +29430,7 @@
     </row>
     <row r="961">
       <c r="A961" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B961" t="s">
         <v>9</v>
@@ -29453,7 +29456,7 @@
     </row>
     <row r="962">
       <c r="A962" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B962" t="s">
         <v>9</v>
@@ -29479,7 +29482,7 @@
     </row>
     <row r="963">
       <c r="A963" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B963" t="s">
         <v>9</v>
@@ -29505,7 +29508,7 @@
     </row>
     <row r="964">
       <c r="A964" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B964" t="s">
         <v>9</v>
@@ -29531,7 +29534,7 @@
     </row>
     <row r="965">
       <c r="A965" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B965" t="s">
         <v>9</v>
@@ -29557,7 +29560,7 @@
     </row>
     <row r="966">
       <c r="A966" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B966" t="s">
         <v>9</v>
@@ -29583,7 +29586,7 @@
     </row>
     <row r="967">
       <c r="A967" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B967" t="s">
         <v>9</v>
@@ -29609,7 +29612,7 @@
     </row>
     <row r="968">
       <c r="A968" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B968" t="s">
         <v>9</v>
@@ -29635,7 +29638,7 @@
     </row>
     <row r="969">
       <c r="A969" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B969" t="s">
         <v>9</v>
@@ -29661,7 +29664,7 @@
     </row>
     <row r="970">
       <c r="A970" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B970" t="s">
         <v>9</v>
@@ -29687,7 +29690,7 @@
     </row>
     <row r="971">
       <c r="A971" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B971" t="s">
         <v>9</v>
@@ -29713,7 +29716,7 @@
     </row>
     <row r="972">
       <c r="A972" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B972" t="s">
         <v>9</v>
@@ -29739,7 +29742,7 @@
     </row>
     <row r="973">
       <c r="A973" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B973" t="s">
         <v>9</v>
@@ -29765,7 +29768,7 @@
     </row>
     <row r="974">
       <c r="A974" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B974" t="s">
         <v>9</v>
@@ -29791,7 +29794,7 @@
     </row>
     <row r="975">
       <c r="A975" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B975" t="s">
         <v>9</v>
@@ -29817,7 +29820,7 @@
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B976" t="s">
         <v>9</v>
@@ -29843,7 +29846,7 @@
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B977" t="s">
         <v>9</v>
@@ -29869,7 +29872,7 @@
     </row>
     <row r="978">
       <c r="A978" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B978" t="s">
         <v>9</v>
@@ -29895,7 +29898,7 @@
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B979" t="s">
         <v>9</v>
@@ -29921,7 +29924,7 @@
     </row>
     <row r="980">
       <c r="A980" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B980" t="s">
         <v>9</v>
@@ -29947,7 +29950,7 @@
     </row>
     <row r="981">
       <c r="A981" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B981" t="s">
         <v>9</v>
@@ -29973,7 +29976,7 @@
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B982" t="s">
         <v>9</v>
@@ -29999,7 +30002,7 @@
     </row>
     <row r="983">
       <c r="A983" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B983" t="s">
         <v>9</v>
@@ -30025,7 +30028,7 @@
     </row>
     <row r="984">
       <c r="A984" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B984" t="s">
         <v>9</v>
@@ -30051,7 +30054,7 @@
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B985" t="s">
         <v>9</v>
@@ -30077,7 +30080,7 @@
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B986" t="s">
         <v>15</v>
@@ -30103,7 +30106,7 @@
     </row>
     <row r="987">
       <c r="A987" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B987" t="s">
         <v>9</v>
@@ -30129,7 +30132,7 @@
     </row>
     <row r="988">
       <c r="A988" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B988" t="s">
         <v>9</v>
@@ -30155,7 +30158,7 @@
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B989" t="s">
         <v>9</v>
@@ -30181,7 +30184,7 @@
     </row>
     <row r="990">
       <c r="A990" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B990" t="s">
         <v>9</v>
